--- a/artfynd/A 27736-2024 artfynd.xlsx
+++ b/artfynd/A 27736-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4898598</v>
+        <v>118957802</v>
       </c>
       <c r="B2" t="n">
-        <v>97308</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222467</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder Lundsjön, Jmt</t>
+          <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475571.7573520116</v>
+        <v>475876</v>
       </c>
       <c r="R2" t="n">
-        <v>7040080.560938525</v>
+        <v>7040078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-06-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-06-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,71 +756,61 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Myr</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5930436</v>
+        <v>118957748</v>
       </c>
       <c r="B3" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söder Lundsjön, Jmt</t>
+          <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475571.7573520116</v>
+        <v>475604</v>
       </c>
       <c r="R3" t="n">
-        <v>7040080.560938525</v>
+        <v>7039996</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-06-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,71 +853,61 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Myr</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2315054</v>
+        <v>118957750</v>
       </c>
       <c r="B4" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder Lundsjön, Jmt</t>
+          <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475571.7573520116</v>
+        <v>475697</v>
       </c>
       <c r="R4" t="n">
-        <v>7040080.560938525</v>
+        <v>7039743</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-06-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-06-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,71 +950,61 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Myr</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2315053</v>
+        <v>118957751</v>
       </c>
       <c r="B5" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder Lundsjön, Jmt</t>
+          <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475563.3356343638</v>
+        <v>475481</v>
       </c>
       <c r="R5" t="n">
-        <v>7040266.050558626</v>
+        <v>7039569</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-06-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-06-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,36 +1047,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>väg/myr</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102344371</v>
+        <v>118957753</v>
       </c>
       <c r="B6" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,41 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222112</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flakamyren, strax N om på skogsbilväg, Jmt</t>
+          <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475578.0355749479</v>
+        <v>475668</v>
       </c>
       <c r="R6" t="n">
-        <v>7040374.507152081</v>
+        <v>7040107</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102344369</v>
+        <v>118957755</v>
       </c>
       <c r="B7" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,41 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221343</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flakamyren, strax N om på skogsbilväg, Jmt</t>
+          <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475578.0355749479</v>
+        <v>475648</v>
       </c>
       <c r="R7" t="n">
-        <v>7040374.507152081</v>
+        <v>7040107</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118957790</v>
+        <v>118957756</v>
       </c>
       <c r="B8" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475519</v>
+        <v>475666</v>
       </c>
       <c r="R8" t="n">
-        <v>7039896</v>
+        <v>7040269</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118957771</v>
+        <v>118957806</v>
       </c>
       <c r="B9" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476019</v>
+        <v>475604</v>
       </c>
       <c r="R9" t="n">
-        <v>7040243</v>
+        <v>7039996</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118957778</v>
+        <v>118957792</v>
       </c>
       <c r="B10" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475415</v>
+        <v>475787</v>
       </c>
       <c r="R10" t="n">
-        <v>7039579</v>
+        <v>7040284</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,19 +1548,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118957798</v>
+        <v>118957793</v>
       </c>
       <c r="B11" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1721,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475635</v>
+        <v>475613</v>
       </c>
       <c r="R11" t="n">
-        <v>7040107</v>
+        <v>7039695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118957750</v>
+        <v>118957794</v>
       </c>
       <c r="B12" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1823,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475697</v>
+        <v>475578</v>
       </c>
       <c r="R12" t="n">
-        <v>7039743</v>
+        <v>7039549</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,19 +1742,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118957793</v>
+        <v>118957795</v>
       </c>
       <c r="B13" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1925,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475613</v>
+        <v>475557</v>
       </c>
       <c r="R13" t="n">
-        <v>7039695</v>
+        <v>7039990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118957768</v>
+        <v>118957796</v>
       </c>
       <c r="B14" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475893</v>
+        <v>475578</v>
       </c>
       <c r="R14" t="n">
-        <v>7040272</v>
+        <v>7040018</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118957789</v>
+        <v>118957797</v>
       </c>
       <c r="B15" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475608</v>
+        <v>475645</v>
       </c>
       <c r="R15" t="n">
-        <v>7039648</v>
+        <v>7040071</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118957751</v>
+        <v>118957798</v>
       </c>
       <c r="B16" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475481</v>
+        <v>475635</v>
       </c>
       <c r="R16" t="n">
-        <v>7039569</v>
+        <v>7040107</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118957779</v>
+        <v>118957799</v>
       </c>
       <c r="B17" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475446</v>
+        <v>475650</v>
       </c>
       <c r="R17" t="n">
-        <v>7039664</v>
+        <v>7040219</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,50 +2227,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118957805</v>
+        <v>115175033</v>
       </c>
       <c r="B18" t="n">
-        <v>100119</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Krokbodarna N, Jmt</t>
+          <t>Krokbodarna NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475664</v>
+        <v>475831</v>
       </c>
       <c r="R18" t="n">
-        <v>7040246</v>
+        <v>7040361</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,12 +2292,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,15 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118957755</v>
+        <v>118957757</v>
       </c>
       <c r="B19" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2513,34 +2340,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475648</v>
+        <v>475734</v>
       </c>
       <c r="R19" t="n">
-        <v>7040107</v>
+        <v>7040296</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,6 +2404,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,15 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118957796</v>
+        <v>118957758</v>
       </c>
       <c r="B20" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2615,34 +2446,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475578</v>
+        <v>475746</v>
       </c>
       <c r="R20" t="n">
-        <v>7040018</v>
+        <v>7040293</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2675,6 +2510,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,15 +2541,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118957788</v>
+        <v>118957760</v>
       </c>
       <c r="B21" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2717,34 +2552,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475593</v>
+        <v>475888</v>
       </c>
       <c r="R21" t="n">
-        <v>7039636</v>
+        <v>7040272</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2777,6 +2616,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2803,15 +2647,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118957794</v>
+        <v>118957761</v>
       </c>
       <c r="B22" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,34 +2658,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475578</v>
+        <v>475840</v>
       </c>
       <c r="R22" t="n">
-        <v>7039549</v>
+        <v>7040058</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,50 +2752,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118957780</v>
+        <v>118957762</v>
       </c>
       <c r="B23" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475525</v>
+        <v>475747</v>
       </c>
       <c r="R23" t="n">
-        <v>7039923</v>
+        <v>7040042</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,6 +2827,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3007,15 +2858,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118957802</v>
+        <v>118957763</v>
       </c>
       <c r="B24" t="n">
-        <v>86829</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3023,34 +2869,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475876</v>
+        <v>475740</v>
       </c>
       <c r="R24" t="n">
-        <v>7040078</v>
+        <v>7040043</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3083,6 +2933,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3109,15 +2964,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118957753</v>
+        <v>118957764</v>
       </c>
       <c r="B25" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,34 +2975,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475668</v>
+        <v>475546</v>
       </c>
       <c r="R25" t="n">
-        <v>7040107</v>
+        <v>7039642</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,6 +3039,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3211,15 +3070,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118957756</v>
+        <v>118957765</v>
       </c>
       <c r="B26" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,34 +3081,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475666</v>
+        <v>475583</v>
       </c>
       <c r="R26" t="n">
-        <v>7040269</v>
+        <v>7039627</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3287,6 +3145,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3313,50 +3176,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118957775</v>
+        <v>118957766</v>
       </c>
       <c r="B27" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475576</v>
+        <v>475709</v>
       </c>
       <c r="R27" t="n">
-        <v>7039825</v>
+        <v>7039637</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3389,6 +3251,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3415,58 +3282,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118957761</v>
+        <v>2315053</v>
       </c>
       <c r="B28" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Krokbodarna N, Jmt</t>
+          <t>Söder Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475840</v>
+        <v>475563</v>
       </c>
       <c r="R28" t="n">
-        <v>7040058</v>
+        <v>7040266</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3493,12 +3347,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2012-06-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2012-06-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3509,66 +3363,66 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>väg/myr</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118957772</v>
+        <v>2315054</v>
       </c>
       <c r="B29" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Krokbodarna N, Jmt</t>
+          <t>Söder Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475960</v>
+        <v>475572</v>
       </c>
       <c r="R29" t="n">
-        <v>7040165</v>
+        <v>7040081</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3595,12 +3449,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2012-06-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2012-06-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3611,31 +3465,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Myr</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118957777</v>
+        <v>118957768</v>
       </c>
       <c r="B30" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475430</v>
+        <v>475893</v>
       </c>
       <c r="R30" t="n">
-        <v>7039560</v>
+        <v>7040272</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,15 +3583,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118957774</v>
+        <v>118957770</v>
       </c>
       <c r="B31" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3769,10 +3618,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475611</v>
+        <v>475960</v>
       </c>
       <c r="R31" t="n">
-        <v>7040001</v>
+        <v>7040244</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3831,37 +3680,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118957795</v>
+        <v>118957771</v>
       </c>
       <c r="B32" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3871,10 +3715,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475557</v>
+        <v>476019</v>
       </c>
       <c r="R32" t="n">
-        <v>7039990</v>
+        <v>7040243</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,15 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118957770</v>
+        <v>118957772</v>
       </c>
       <c r="B33" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3976,7 +3815,7 @@
         <v>475960</v>
       </c>
       <c r="R33" t="n">
-        <v>7040244</v>
+        <v>7040165</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,37 +3874,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118957748</v>
+        <v>118957773</v>
       </c>
       <c r="B34" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4075,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475604</v>
+        <v>475751</v>
       </c>
       <c r="R34" t="n">
-        <v>7039996</v>
+        <v>7040051</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4137,15 +3971,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118957806</v>
+        <v>118957774</v>
       </c>
       <c r="B35" t="n">
-        <v>90856</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4153,21 +3982,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4177,10 +4006,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475604</v>
+        <v>475611</v>
       </c>
       <c r="R35" t="n">
-        <v>7039996</v>
+        <v>7040001</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4239,54 +4068,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118957764</v>
+        <v>118957775</v>
       </c>
       <c r="B36" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475546</v>
+        <v>475576</v>
       </c>
       <c r="R36" t="n">
-        <v>7039642</v>
+        <v>7039825</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4319,11 +4139,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,37 +4165,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118957797</v>
+        <v>118957776</v>
       </c>
       <c r="B37" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4390,10 +4200,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475645</v>
+        <v>475682</v>
       </c>
       <c r="R37" t="n">
-        <v>7040071</v>
+        <v>7039743</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4452,54 +4262,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118957757</v>
+        <v>118957777</v>
       </c>
       <c r="B38" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475734</v>
+        <v>475430</v>
       </c>
       <c r="R38" t="n">
-        <v>7040296</v>
+        <v>7039560</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4532,11 +4333,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4563,15 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118957776</v>
+        <v>118957778</v>
       </c>
       <c r="B39" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4603,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475682</v>
+        <v>475415</v>
       </c>
       <c r="R39" t="n">
-        <v>7039743</v>
+        <v>7039579</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4665,54 +4456,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118957763</v>
+        <v>118957779</v>
       </c>
       <c r="B40" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475740</v>
+        <v>475446</v>
       </c>
       <c r="R40" t="n">
-        <v>7040043</v>
+        <v>7039664</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4745,11 +4527,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4776,54 +4553,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118957760</v>
+        <v>118957780</v>
       </c>
       <c r="B41" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475888</v>
+        <v>475525</v>
       </c>
       <c r="R41" t="n">
-        <v>7040272</v>
+        <v>7039923</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4856,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4887,37 +4650,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118957792</v>
+        <v>118957781</v>
       </c>
       <c r="B42" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4927,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475787</v>
+        <v>475575</v>
       </c>
       <c r="R42" t="n">
-        <v>7040284</v>
+        <v>7040007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,54 +4747,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118957765</v>
+        <v>118957782</v>
       </c>
       <c r="B43" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475583</v>
+        <v>475641</v>
       </c>
       <c r="R43" t="n">
-        <v>7039627</v>
+        <v>7040071</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5069,11 +4818,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5100,15 +4844,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118957782</v>
+        <v>118957784</v>
       </c>
       <c r="B44" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5140,10 +4879,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475641</v>
+        <v>475637</v>
       </c>
       <c r="R44" t="n">
-        <v>7040071</v>
+        <v>7040210</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5202,15 +4941,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118957799</v>
+        <v>102344369</v>
       </c>
       <c r="B45" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5218,37 +4952,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>221343</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Krokbodarna N, Jmt</t>
+          <t>Flakamyren, strax N om på skogsbilväg, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475650</v>
+        <v>475578</v>
       </c>
       <c r="R45" t="n">
-        <v>7040219</v>
+        <v>7040375</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5272,12 +5010,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5292,65 +5030,64 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118957804</v>
+        <v>102344371</v>
       </c>
       <c r="B46" t="n">
-        <v>100119</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>222112</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Krokbodarna N, Jmt</t>
+          <t>Flakamyren, strax N om på skogsbilväg, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475528</v>
+        <v>475578</v>
       </c>
       <c r="R46" t="n">
-        <v>7039911</v>
+        <v>7040375</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5374,12 +5111,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5394,66 +5131,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118957762</v>
+        <v>4898598</v>
       </c>
       <c r="B47" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100143</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>222467</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Krokbodarna N, Jmt</t>
+          <t>Söder Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475747</v>
+        <v>475572</v>
       </c>
       <c r="R47" t="n">
-        <v>7040042</v>
+        <v>7040081</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5480,17 +5208,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2012-06-15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2012-06-15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5501,53 +5224,53 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Myr</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118957781</v>
+        <v>118957804</v>
       </c>
       <c r="B48" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5557,10 +5280,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475575</v>
+        <v>475528</v>
       </c>
       <c r="R48" t="n">
-        <v>7040007</v>
+        <v>7039911</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5619,54 +5342,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118957766</v>
+        <v>118957805</v>
       </c>
       <c r="B49" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Krokbodarna N, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475709</v>
+        <v>475664</v>
       </c>
       <c r="R49" t="n">
-        <v>7039637</v>
+        <v>7040246</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5699,11 +5413,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5730,54 +5439,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118957758</v>
+        <v>5930436</v>
       </c>
       <c r="B50" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99036</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>223591</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Krokbodarna N, Jmt</t>
+          <t>Söder Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475746</v>
+        <v>475572</v>
       </c>
       <c r="R50" t="n">
-        <v>7040293</v>
+        <v>7040081</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5804,17 +5504,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2012-06-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2012-06-15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5825,325 +5520,24 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Myr</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>118957784</v>
-      </c>
-      <c r="B51" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Krokbodarna N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>475637</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7040210</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>118957787</v>
-      </c>
-      <c r="B52" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Krokbodarna N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>475745</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7040295</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>118957773</v>
-      </c>
-      <c r="B53" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Krokbodarna N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>475751</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7040051</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27736-2024 artfynd.xlsx
+++ b/artfynd/A 27736-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957802</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957748</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957750</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957751</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957753</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957755</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957756</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957806</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957792</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957793</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957794</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957795</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957796</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957797</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957798</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957799</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115175033</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2432,6 +2522,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957757</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2538,6 +2633,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957758</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2644,6 +2744,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957760</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2749,6 +2854,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957761</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2855,6 +2965,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957762</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2961,6 +3076,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957763</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3067,6 +3187,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957764</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3173,6 +3298,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957765</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3279,6 +3409,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957766</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3381,6 +3516,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2315053</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3483,6 +3623,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2315054</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3580,6 +3725,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957768</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3677,6 +3827,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957770</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3774,6 +3929,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957771</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3871,6 +4031,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957772</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3968,6 +4133,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957773</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4065,6 +4235,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957774</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4162,6 +4337,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957775</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4259,6 +4439,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957776</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4356,6 +4541,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957777</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4453,6 +4643,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957778</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4550,6 +4745,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957779</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4647,6 +4847,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957780</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4744,6 +4949,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957781</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4841,6 +5051,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957782</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4938,6 +5153,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957784</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5039,6 +5259,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102344369</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5140,6 +5365,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102344371</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5242,6 +5472,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4898598</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5339,6 +5574,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957804</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5436,6 +5676,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118957805</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5538,8 +5783,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5930436</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>